--- a/reports/devops-jobs-israel-2026-W42.xlsx
+++ b/reports/devops-jobs-israel-2026-W42.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="508">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-12T15:11:09</t>
+    <t xml:space="preserve">2026-10-13T14:02:48</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -528,6 +528,21 @@
     <t xml:space="preserve">2026-09-21</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-shavit-software-4478756927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevOps</t>
   </si>
   <si>
@@ -540,9 +555,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-paypal-4478324728</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vectorious Medical Technologies</t>
   </si>
   <si>
@@ -555,295 +567,517 @@
     <t xml:space="preserve">2026-10-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Platform Engineer- CTI</t>
+    <t xml:space="preserve">DevOps Engineer (25769)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37726)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37726-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478516288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478503786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475656469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4475688590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4478307184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-abra-4477991175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4478094744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4477987658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4478312027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4478376789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-for-security-team-at-lenovo-4477907387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE / DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">april</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AITAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4478069626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4478771513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Integrator SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-compie-technologies-4477142119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
   </si>
   <si>
     <t xml:space="preserve">Dream</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-cti-at-dream-4465727084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25769)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37726)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37726-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478516288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478503786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gini-apps-4476189127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475656469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4475688590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4478307184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4478094744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4478376789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer, Graviton Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4475682981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
   </si>
   <si>
     <t xml:space="preserve">Raanana, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-4474645372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AITAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4478069626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4478313160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4476701773</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraCyte Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackEdge Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-labs-4477122203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer #8106</t>
@@ -855,226 +1089,70 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
   </si>
   <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Integrator SRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-compie-technologies-4477142119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Infrastructure Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yanolja Go Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-team-lead-at-yanolja-go-global-4475903431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4475682981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineering Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineering-team-lead-at-corsa-4476174341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraCyte Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI &amp; Software Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BioCatch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-software-infra-engineer-at-biocatch-4447894244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackEdge Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-labs-4477122203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G-STAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-g-stat-4474677345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-platform-engineer-ai-security-team-at-lenovo-4477568550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4475262509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4476089690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478504540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
   </si>
   <si>
     <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
@@ -1089,135 +1167,33 @@
     <t xml:space="preserve">2026-08-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Cloud Engineer (GCP Focus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MyOps by Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-gcp-focus-at-myops-by-yael-group-4477131302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-elbit-systems-israel-4474036853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478504540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -1254,10 +1230,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7%</t>
+    <t xml:space="preserve">52.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1401,24 +1377,12 @@
     <t xml:space="preserve">Software Engineer Student, SPIV team</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
     <t xml:space="preserve">Production Operations Engineer</t>
   </si>
   <si>
@@ -1473,15 +1437,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
   </si>
   <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -1506,6 +1461,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Docker, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4476025268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4478393138</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Engineering INTERN</t>
   </si>
   <si>
@@ -1524,19 +1500,19 @@
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Terraform/IaC</t>
@@ -1691,7 +1667,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7">
@@ -1699,7 +1675,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1787,7 +1763,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20">
@@ -1814,28 +1790,28 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="B3" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1843,7 +1819,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1851,7 +1827,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1859,7 +1835,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1878,15 +1854,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
@@ -1894,7 +1870,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B3" s="3">
         <v>24</v>
@@ -1902,15 +1878,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>504</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -1918,15 +1894,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>399</v>
+        <v>496</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>315</v>
+        <v>497</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
@@ -1934,47 +1910,47 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>505</v>
+        <v>391</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -1982,7 +1958,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -1990,7 +1966,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
@@ -1998,7 +1974,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -2026,13 +2002,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2">
@@ -2043,10 +2019,10 @@
         <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>12.0</v>
+        <v>13.3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2055,88 +2031,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>45.4</v>
+        <v>37.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.1</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>34.2</v>
+        <v>31.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>16.5</v>
+        <v>15.1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.7</v>
+        <v>19.6</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2220,7 +2196,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2252,7 +2228,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2284,7 +2260,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2316,7 +2292,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -2348,7 +2324,7 @@
         <v>51</v>
       </c>
       <c r="J6" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -2380,7 +2356,7 @@
         <v>58</v>
       </c>
       <c r="J7" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -2412,7 +2388,7 @@
         <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -2444,7 +2420,7 @@
         <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -2476,7 +2452,7 @@
         <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -2508,7 +2484,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -2540,7 +2516,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -2572,7 +2548,7 @@
         <v>83</v>
       </c>
       <c r="J13" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2604,7 +2580,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2636,7 +2612,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2668,7 +2644,7 @@
         <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -2700,7 +2676,7 @@
         <v>101</v>
       </c>
       <c r="J17" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -2732,7 +2708,7 @@
         <v>91</v>
       </c>
       <c r="J18" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -2764,7 +2740,7 @@
         <v>64</v>
       </c>
       <c r="J19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -2796,7 +2772,7 @@
         <v>111</v>
       </c>
       <c r="J20" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -2828,7 +2804,7 @@
         <v>117</v>
       </c>
       <c r="J21" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -2860,7 +2836,7 @@
         <v>87</v>
       </c>
       <c r="J22" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -2892,7 +2868,7 @@
         <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -2924,7 +2900,7 @@
         <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2956,7 +2932,7 @@
         <v>134</v>
       </c>
       <c r="J25" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26">
@@ -2988,7 +2964,7 @@
         <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -3018,7 +2994,7 @@
         <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -3050,7 +3026,7 @@
         <v>148</v>
       </c>
       <c r="J28" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
@@ -3082,7 +3058,7 @@
         <v>51</v>
       </c>
       <c r="J29" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
@@ -3114,7 +3090,7 @@
         <v>76</v>
       </c>
       <c r="J30" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
@@ -3146,7 +3122,7 @@
         <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
@@ -3176,7 +3152,7 @@
         <v>168</v>
       </c>
       <c r="J32" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -3190,10 +3166,10 @@
         <v>171</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
@@ -3203,7 +3179,7 @@
         <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -3211,29 +3187,29 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="J34" s="3">
         <v>1</v>
@@ -3241,19 +3217,19 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D35" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
@@ -3263,21 +3239,21 @@
         <v>180</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="J35" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
@@ -3290,24 +3266,24 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>117</v>
       </c>
       <c r="J36" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>141</v>
@@ -3320,24 +3296,24 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J37" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>48</v>
@@ -3350,24 +3326,24 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J38" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>48</v>
@@ -3376,30 +3352,30 @@
         <v>42</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J39" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>141</v>
@@ -3412,24 +3388,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J40" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>48</v>
@@ -3442,24 +3418,24 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>76</v>
       </c>
       <c r="J41" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>48</v>
@@ -3472,30 +3448,30 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="J42" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3505,7 +3481,7 @@
         <v>204</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="J43" s="3">
         <v>1</v>
@@ -3513,29 +3489,29 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>205</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>55</v>
+        <v>206</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -3543,13 +3519,13 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>48</v>
@@ -3565,24 +3541,24 @@
         <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="J45" s="3">
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>37</v>
@@ -3592,24 +3568,24 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>111</v>
+        <v>181</v>
       </c>
       <c r="J46" s="3">
-        <v>45</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>141</v>
@@ -3625,10 +3601,10 @@
         <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3639,13 +3615,13 @@
         <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
@@ -3655,40 +3631,40 @@
         <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>46</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="J49" s="3">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3699,7 +3675,7 @@
         <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>48</v>
@@ -3715,21 +3691,21 @@
         <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="J50" s="3">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>223</v>
+        <v>46</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>48</v>
@@ -3745,97 +3721,97 @@
         <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="J51" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>173</v>
+        <v>226</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>231</v>
+        <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J53" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>173</v>
+        <v>231</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="J54" s="3">
         <v>0</v>
@@ -3843,16 +3819,16 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>237</v>
+        <v>176</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>231</v>
+        <v>48</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>37</v>
@@ -3862,87 +3838,89 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="J55" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="J57" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3952,54 +3930,54 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J58" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D59" s="3" t="s">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="J59" s="3">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
@@ -4012,27 +3990,27 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>255</v>
+        <v>179</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>231</v>
+        <v>48</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>37</v>
@@ -4042,59 +4020,57 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="J61" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>261</v>
+        <v>179</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>262</v>
+        <v>48</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>37</v>
@@ -4104,70 +4080,72 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>250</v>
+        <v>117</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>171</v>
+        <v>261</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="J64" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>41</v>
+        <v>263</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="J65" s="3">
         <v>1</v>
@@ -4175,16 +4153,16 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>175</v>
+        <v>266</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>48</v>
+        <v>267</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>37</v>
@@ -4194,30 +4172,30 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>177</v>
+        <v>257</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>237</v>
+        <v>176</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>231</v>
+        <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
@@ -4227,54 +4205,54 @@
         <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="J67" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>173</v>
+        <v>41</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>273</v>
+        <v>206</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="J68" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>275</v>
+        <v>169</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>276</v>
+        <v>246</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>175</v>
+        <v>247</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>37</v>
@@ -4284,24 +4262,24 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J69" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>278</v>
+        <v>169</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>48</v>
@@ -4314,51 +4292,51 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>281</v>
+        <v>173</v>
       </c>
       <c r="J70" s="3">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="J71" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>283</v>
@@ -4374,57 +4352,57 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>87</v>
+        <v>192</v>
       </c>
       <c r="J72" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>292</v>
+        <v>179</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>37</v>
@@ -4434,27 +4412,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="J74" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>179</v>
+        <v>291</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>171</v>
+        <v>292</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4464,54 +4442,54 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>296</v>
+        <v>129</v>
       </c>
       <c r="J75" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>299</v>
+        <v>176</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>177</v>
+        <v>297</v>
       </c>
       <c r="J76" s="3">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>48</v>
@@ -4524,24 +4502,24 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J77" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>305</v>
+        <v>241</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>48</v>
@@ -4554,10 +4532,10 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="J78" s="3">
         <v>0</v>
@@ -4565,105 +4543,103 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="J79" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="J80" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>312</v>
+        <v>46</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>314</v>
+        <v>176</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>315</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="J81" s="3">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>141</v>
@@ -4671,29 +4647,31 @@
       <c r="E82" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>52</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>48</v>
@@ -4706,116 +4684,116 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J83" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J84" s="3">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>326</v>
+        <v>46</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>319</v>
+        <v>266</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>141</v>
+        <v>267</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>327</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>250</v>
+        <v>123</v>
       </c>
       <c r="J85" s="3">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>171</v>
+        <v>327</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>143</v>
       </c>
       <c r="J86" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>48</v>
@@ -4828,57 +4806,57 @@
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>58</v>
       </c>
       <c r="J87" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>175</v>
+        <v>337</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>37</v>
@@ -4888,24 +4866,24 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>117</v>
       </c>
       <c r="J89" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>173</v>
+        <v>339</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>141</v>
@@ -4913,61 +4891,61 @@
       <c r="E90" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="J90" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>171</v>
+        <v>341</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>345</v>
+        <v>52</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>346</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>48</v>
@@ -4983,24 +4961,24 @@
         <v>347</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="J92" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>348</v>
+        <v>179</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>231</v>
+        <v>48</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>37</v>
@@ -5010,75 +4988,73 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>46</v>
+        <v>351</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>262</v>
+        <v>36</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="J94" s="3">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>327</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>355</v>
+        <v>129</v>
       </c>
       <c r="J95" s="3">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -5089,42 +5065,40 @@
         <v>357</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>358</v>
+        <v>166</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>141</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>359</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J96" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>363</v>
+        <v>176</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>42</v>
@@ -5134,57 +5108,59 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>143</v>
       </c>
       <c r="J97" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>243</v>
+        <v>327</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J98" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>37</v>
@@ -5194,10 +5170,10 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="J99" s="3">
         <v>0</v>
@@ -5205,43 +5181,43 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>372</v>
+        <v>186</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J100" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>375</v>
+        <v>206</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>48</v>
@@ -5254,24 +5230,24 @@
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>202</v>
+        <v>117</v>
       </c>
       <c r="J101" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>363</v>
+        <v>187</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>141</v>
@@ -5279,144 +5255,84 @@
       <c r="E102" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>315</v>
-      </c>
+      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>186</v>
+        <v>283</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>141</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>129</v>
+        <v>377</v>
       </c>
       <c r="J103" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F104" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="G104" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>117</v>
+        <v>381</v>
       </c>
       <c r="J104" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J105" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="J106" s="3">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J106"/>
+  <autoFilter ref="A1:J104"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5521,8 +5437,6 @@
     <hyperlink ref="H102" r:id="rId101"/>
     <hyperlink ref="H103" r:id="rId102"/>
     <hyperlink ref="H104" r:id="rId103"/>
-    <hyperlink ref="H105" r:id="rId104"/>
-    <hyperlink ref="H106" r:id="rId105"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5530,8 +5444,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5564,21 +5478,21 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3">
@@ -5586,10 +5500,10 @@
         <v>169</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5597,18 +5511,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5616,18 +5530,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5635,18 +5549,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>231</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>176</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5654,18 +5568,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5673,18 +5587,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5692,18 +5606,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5711,18 +5625,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5730,18 +5644,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5749,18 +5663,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>277</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>292</v>
+        <v>176</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5768,18 +5682,18 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>173</v>
+        <v>351</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>175</v>
+        <v>337</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5787,18 +5701,18 @@
         <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>306</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5806,87 +5720,11 @@
         <v>22</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5901,10 +5739,6 @@
     <hyperlink ref="G12" r:id="rId11"/>
     <hyperlink ref="G13" r:id="rId12"/>
     <hyperlink ref="G14" r:id="rId13"/>
-    <hyperlink ref="G15" r:id="rId14"/>
-    <hyperlink ref="G16" r:id="rId15"/>
-    <hyperlink ref="G17" r:id="rId16"/>
-    <hyperlink ref="G18" r:id="rId17"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5918,15 +5752,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B2" s="3">
         <v>22</v>
@@ -5934,7 +5768,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5942,7 +5776,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B4" s="3">
         <v>21</v>
@@ -5950,23 +5784,23 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>359</v>
+        <v>132</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5974,7 +5808,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5982,7 +5816,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>315</v>
+        <v>389</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5990,15 +5824,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>397</v>
+        <v>314</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -6006,7 +5840,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -6014,7 +5848,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B13" s="3">
         <v>10</v>
@@ -6022,7 +5856,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -6030,7 +5864,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -6038,7 +5872,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -6060,7 +5894,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
@@ -6081,15 +5915,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>242</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6097,7 +5931,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6105,7 +5939,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>113</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -6113,7 +5947,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -6121,7 +5955,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>185</v>
+        <v>241</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -6129,7 +5963,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
@@ -6137,15 +5971,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>282</v>
       </c>
       <c r="B11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -6153,7 +5987,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -6161,7 +5995,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>258</v>
+        <v>170</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6169,7 +6003,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>291</v>
+        <v>190</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6177,7 +6011,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6198,16 +6032,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
@@ -6299,13 +6133,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C8" s="3">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6313,10 +6147,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="C9" s="3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -6327,13 +6161,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>216</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6341,13 +6175,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6355,7 +6189,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>236</v>
+        <v>186</v>
       </c>
       <c r="C12" s="3">
         <v>3.6</v>
@@ -6369,13 +6203,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
       <c r="C13" s="3">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6383,10 +6217,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>145</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -6397,13 +6231,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="C15" s="3">
         <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6411,7 +6245,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6437,21 +6271,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3">
@@ -6459,10 +6293,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4">
@@ -6473,7 +6307,7 @@
         <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -6492,7 +6326,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -6500,7 +6334,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -6508,20 +6342,20 @@
         <v>141</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>231</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6529,7 +6363,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B6" s="3">
         <v>2</v>
@@ -6564,10 +6398,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6579,10 +6413,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6599,31 +6433,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3">
@@ -6631,31 +6465,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4">
@@ -6663,28 +6497,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>243</v>
+        <v>337</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>83</v>
@@ -6695,28 +6529,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>83</v>
@@ -6727,31 +6561,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="F6" s="3">
         <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
@@ -6759,31 +6593,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="F7" s="3">
         <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8">
@@ -6791,31 +6625,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>283</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="F8" s="3">
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -6823,28 +6657,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F9" s="3">
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>117</v>
@@ -6855,31 +6689,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="F10" s="3">
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11">
@@ -6887,31 +6721,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F11" s="3">
         <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12">
@@ -6919,28 +6753,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>460</v>
+        <v>305</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F12" s="3">
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>83</v>
@@ -6951,31 +6785,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>243</v>
+        <v>456</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="F13" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>143</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14">
@@ -6983,31 +6817,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>468</v>
+        <v>176</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="F14" s="3">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>471</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -7015,31 +6849,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>473</v>
+        <v>299</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>171</v>
+        <v>247</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>474</v>
+        <v>431</v>
       </c>
       <c r="F15" s="3">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
@@ -7047,31 +6881,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>302</v>
+        <v>469</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>237</v>
+        <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="F16" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17">
@@ -7079,31 +6913,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="E17" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="F17" s="3">
+        <v>46</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="F17" s="3">
-        <v>54</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>482</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>250</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -7111,31 +6945,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>288</v>
+        <v>477</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F18" s="3">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>143</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19">
@@ -7143,31 +6977,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="F19" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -7175,31 +7009,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>491</v>
+        <v>311</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>492</v>
+        <v>170</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>171</v>
+        <v>484</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>442</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
@@ -7207,28 +7041,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F21" s="3">
         <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>83</v>

--- a/reports/devops-jobs-israel-2026-W42.xlsx
+++ b/reports/devops-jobs-israel-2026-W42.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-13T14:02:48</t>
+    <t xml:space="preserve">2026-10-14T11:40:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -453,64 +453,82 @@
     <t xml:space="preserve">2026-10-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4478174885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Axonius</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devex-devops-engineer-at-axonius-4446639008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blockaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4478435119</t>
   </si>
   <si>
     <t xml:space="preserve">Sr. Principal, DevOps</t>
@@ -549,24 +567,24 @@
     <t xml:space="preserve">PayPal</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-paypal-4478324728</t>
   </si>
   <si>
     <t xml:space="preserve">Vectorious Medical Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4478097565</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-11</t>
   </si>
   <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer (25769)</t>
   </si>
   <si>
@@ -588,21 +606,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37726-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478516288</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+    <t xml:space="preserve">Senior DevOps Engineer-5692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrypoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-5692-at-entrypoint-4478139921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
   </si>
   <si>
     <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
@@ -615,6 +636,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478503786</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4479012298</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
   </si>
   <si>
@@ -636,13 +666,256 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4475688590</t>
   </si>
   <si>
-    <t xml:space="preserve">Checkmarx</t>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4478427154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4478312027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-abra-4477991175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-for-security-team-at-lenovo-4477907387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4477987658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4478376789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4476644367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitsight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
   </si>
   <si>
     <t xml:space="preserve">Connecteam</t>
@@ -651,28 +924,28 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
   </si>
   <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4478307184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-abra-4477991175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
+    <t xml:space="preserve">System Engineer, Graviton Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zscaler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4475682981</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
@@ -684,130 +957,205 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4478094744</t>
   </si>
   <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4477987658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4478312027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4478376789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-for-security-team-at-lenovo-4477907387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4475164979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4474071911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraCyte Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlackEdge Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-labs-4477122203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer #8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4476650305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4476089690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478504540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
@@ -816,703 +1164,370 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
   </si>
   <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AITAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-aitan-4478069626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-medulla-4478771513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Integrator SRE</t>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
     <t xml:space="preserve">Compie Technologies</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-integrator-sre-at-compie-technologies-4477142119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer, Graviton Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4475682981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Network &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-network-devops-engineer-at-applied-materials-israel-4474407748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraCyte Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackEdge Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-labs-4477122203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer #8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer - Proxy Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nimble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-proxy-network-at-nimble-4475424343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4476089690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478504540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4478769750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPD Hosting LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-spd-hosting-ltd-4476095499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4476025268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4478393138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
+    <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
   </si>
   <si>
     <t xml:space="preserve">Terraform/IaC</t>
@@ -1667,7 +1682,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -1675,7 +1690,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1683,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1691,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>871</v>
+        <v>864</v>
       </c>
     </row>
     <row r="10">
@@ -1771,7 +1786,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1790,36 +1805,36 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>462</v>
+        <v>412</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -1827,7 +1842,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>416</v>
+        <v>495</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1835,7 +1850,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1854,95 +1869,95 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>394</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>391</v>
+        <v>502</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -1953,28 +1968,28 @@
         <v>389</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>387</v>
+        <v>503</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>498</v>
+        <v>391</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -2002,13 +2017,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2">
@@ -2016,13 +2031,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>13.3</v>
+        <v>11.6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2034,85 +2049,85 @@
         <v>75</v>
       </c>
       <c r="C3" s="3">
-        <v>37.0</v>
+        <v>61.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.0</v>
+        <v>7.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.0</v>
+        <v>32.5</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.1</v>
+        <v>14.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2196,7 +2211,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2228,7 +2243,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2260,7 +2275,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -2292,7 +2307,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -2324,7 +2339,7 @@
         <v>51</v>
       </c>
       <c r="J6" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -2356,7 +2371,7 @@
         <v>58</v>
       </c>
       <c r="J7" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -2388,7 +2403,7 @@
         <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -2420,7 +2435,7 @@
         <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -2452,7 +2467,7 @@
         <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -2484,7 +2499,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -2516,7 +2531,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -2548,7 +2563,7 @@
         <v>83</v>
       </c>
       <c r="J13" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2580,7 +2595,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2612,7 +2627,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2644,7 +2659,7 @@
         <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -2676,7 +2691,7 @@
         <v>101</v>
       </c>
       <c r="J17" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -2708,7 +2723,7 @@
         <v>91</v>
       </c>
       <c r="J18" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -2740,7 +2755,7 @@
         <v>64</v>
       </c>
       <c r="J19" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -2772,7 +2787,7 @@
         <v>111</v>
       </c>
       <c r="J20" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
@@ -2804,7 +2819,7 @@
         <v>117</v>
       </c>
       <c r="J21" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -2836,7 +2851,7 @@
         <v>87</v>
       </c>
       <c r="J22" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -2868,7 +2883,7 @@
         <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
@@ -2900,7 +2915,7 @@
         <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2932,7 +2947,7 @@
         <v>134</v>
       </c>
       <c r="J25" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
@@ -2964,7 +2979,7 @@
         <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -2994,7 +3009,7 @@
         <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -3005,7 +3020,7 @@
         <v>145</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>48</v>
@@ -3014,19 +3029,19 @@
         <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="J28" s="3">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -3040,7 +3055,7 @@
         <v>151</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>42</v>
@@ -3055,10 +3070,10 @@
         <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="J29" s="3">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
@@ -3069,28 +3084,28 @@
         <v>155</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="J30" s="3">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
@@ -3101,7 +3116,7 @@
         <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>48</v>
@@ -3109,11 +3124,9 @@
       <c r="E31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>161</v>
-      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>162</v>
@@ -3122,7 +3135,7 @@
         <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3136,7 +3149,7 @@
         <v>166</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>42</v>
@@ -3149,37 +3162,37 @@
         <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J32" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -3187,16 +3200,16 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>42</v>
@@ -3206,27 +3219,27 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>37</v>
@@ -3236,57 +3249,57 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J36" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>37</v>
@@ -3296,86 +3309,84 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="J38" s="3">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="I39" s="3" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="J39" s="3">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>141</v>
@@ -3388,24 +3399,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>48</v>
@@ -3418,32 +3429,34 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="J41" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
@@ -3451,27 +3464,27 @@
         <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>181</v>
+        <v>87</v>
       </c>
       <c r="J42" s="3">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3484,21 +3497,21 @@
         <v>129</v>
       </c>
       <c r="J43" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>37</v>
@@ -3511,7 +3524,7 @@
         <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="J44" s="3">
         <v>0</v>
@@ -3519,46 +3532,46 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="J45" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>37</v>
@@ -3568,30 +3581,30 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J46" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>144</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>213</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3601,37 +3614,37 @@
         <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="J48" s="3">
         <v>0</v>
@@ -3639,13 +3652,13 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>48</v>
@@ -3658,24 +3671,24 @@
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>46</v>
+        <v>219</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>48</v>
@@ -3688,27 +3701,27 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="J50" s="3">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>46</v>
+        <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>42</v>
@@ -3721,54 +3734,54 @@
         <v>225</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="J51" s="3">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="J52" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>37</v>
@@ -3778,24 +3791,24 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>231</v>
+        <v>46</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -3808,24 +3821,24 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>48</v>
@@ -3838,32 +3851,34 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
@@ -3871,7 +3886,7 @@
         <v>239</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="J56" s="3">
         <v>1</v>
@@ -3882,10 +3897,10 @@
         <v>240</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
@@ -3893,34 +3908,32 @@
       <c r="E57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>194</v>
-      </c>
+      <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>243</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3933,54 +3946,54 @@
         <v>244</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>129</v>
+        <v>245</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>249</v>
+        <v>129</v>
       </c>
       <c r="J59" s="3">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>37</v>
@@ -3990,27 +4003,27 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="J60" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>169</v>
+        <v>253</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>179</v>
+        <v>255</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>48</v>
+        <v>249</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>37</v>
@@ -4020,24 +4033,24 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>143</v>
+        <v>257</v>
       </c>
       <c r="J61" s="3">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>48</v>
@@ -4050,24 +4063,24 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>48</v>
@@ -4080,27 +4093,27 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="I63" s="3" t="s">
         <v>117</v>
       </c>
       <c r="J63" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>37</v>
@@ -4110,24 +4123,24 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>48</v>
@@ -4135,94 +4148,92 @@
       <c r="E65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>194</v>
-      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>129</v>
+        <v>270</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>267</v>
+        <v>141</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>257</v>
+        <v>87</v>
       </c>
       <c r="J66" s="3">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>176</v>
+        <v>276</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="J67" s="3">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>41</v>
+        <v>278</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>206</v>
+        <v>280</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>42</v>
@@ -4232,27 +4243,27 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>181</v>
+        <v>282</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>169</v>
+        <v>283</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>247</v>
+        <v>166</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>37</v>
@@ -4262,144 +4273,144 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>137</v>
+        <v>286</v>
       </c>
       <c r="J69" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>278</v>
+        <v>160</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>176</v>
+        <v>272</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="J71" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>192</v>
+        <v>296</v>
       </c>
       <c r="J72" s="3">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>283</v>
+        <v>166</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="J73" s="3">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>287</v>
+        <v>175</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>48</v>
@@ -4412,27 +4423,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J74" s="3">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>141</v>
+        <v>249</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4442,10 +4453,10 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="J75" s="3">
         <v>1</v>
@@ -4453,29 +4464,29 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>297</v>
+        <v>71</v>
       </c>
       <c r="J76" s="3">
         <v>34</v>
@@ -4483,13 +4494,13 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>298</v>
+        <v>175</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>48</v>
@@ -4502,24 +4513,24 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>301</v>
+        <v>129</v>
       </c>
       <c r="J77" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>241</v>
+        <v>310</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>48</v>
@@ -4532,84 +4543,86 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J78" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>304</v>
+        <v>46</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>237</v>
+        <v>166</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>169</v>
+        <v>314</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>179</v>
+        <v>316</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>46</v>
+        <v>319</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>48</v>
@@ -4622,151 +4635,149 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="J81" s="3">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>311</v>
+        <v>52</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>313</v>
+        <v>166</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>314</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J82" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>176</v>
+        <v>326</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>247</v>
+        <v>166</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>238</v>
+        <v>48</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>320</v>
-      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="J84" s="3">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>46</v>
+        <v>331</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>266</v>
+        <v>326</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>267</v>
+        <v>141</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>332</v>
+      </c>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>123</v>
+        <v>261</v>
       </c>
       <c r="J85" s="3">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>327</v>
+        <v>166</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>42</v>
@@ -4776,57 +4787,59 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="J86" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>176</v>
+        <v>255</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>48</v>
+        <v>249</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>58</v>
+        <v>340</v>
       </c>
       <c r="J87" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>332</v>
+        <v>46</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>42</v>
@@ -4836,24 +4849,24 @@
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J88" s="3">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>36</v>
@@ -4866,59 +4879,57 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>117</v>
       </c>
       <c r="J89" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>341</v>
+        <v>166</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>342</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>257</v>
+        <v>117</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>344</v>
+        <v>175</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>37</v>
@@ -4928,57 +4939,57 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="J91" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>52</v>
+        <v>352</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>181</v>
+        <v>117</v>
       </c>
       <c r="J92" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>349</v>
+        <v>220</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>179</v>
+        <v>345</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>37</v>
@@ -4988,27 +4999,27 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="J93" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>216</v>
+        <v>358</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>337</v>
+        <v>161</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -5018,54 +5029,54 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>354</v>
+        <v>200</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="J95" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>141</v>
@@ -5078,72 +5089,72 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J96" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>176</v>
+        <v>367</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F97" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J97" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>327</v>
+        <v>161</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>314</v>
-      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="J98" s="3">
         <v>1</v>
@@ -5151,13 +5162,13 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>366</v>
+        <v>176</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>179</v>
+        <v>294</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>48</v>
@@ -5170,24 +5181,24 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>141</v>
@@ -5200,27 +5211,27 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J100" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>170</v>
+        <v>377</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>37</v>
@@ -5230,109 +5241,79 @@
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>117</v>
       </c>
       <c r="J101" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>373</v>
+        <v>238</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F102" s="3"/>
+      <c r="F102" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="G102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J102" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>282</v>
+        <v>382</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F103" s="3"/>
       <c r="G103" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="J103" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="J104" s="3">
-        <v>61</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J104"/>
+  <autoFilter ref="A1:J103"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5436,7 +5417,6 @@
     <hyperlink ref="H101" r:id="rId100"/>
     <hyperlink ref="H102" r:id="rId101"/>
     <hyperlink ref="H103" r:id="rId102"/>
-    <hyperlink ref="H104" r:id="rId103"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5444,8 +5424,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5478,13 +5458,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5492,18 +5472,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5511,18 +5491,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>212</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5530,18 +5510,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5549,18 +5529,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5568,18 +5548,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5587,18 +5567,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>240</v>
+        <v>175</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5606,18 +5586,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5625,18 +5605,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>176</v>
+        <v>223</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5644,87 +5624,11 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5735,10 +5639,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5752,42 +5652,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -5795,28 +5695,28 @@
         <v>132</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5824,15 +5724,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>314</v>
+        <v>393</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5840,23 +5740,23 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5864,7 +5764,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5872,7 +5772,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5894,7 +5794,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -5939,7 +5839,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5947,7 +5847,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5955,7 +5855,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5963,7 +5863,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
@@ -5971,7 +5871,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
       <c r="B11" s="3">
         <v>3</v>
@@ -5995,7 +5895,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -6003,7 +5903,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>190</v>
+        <v>254</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -6011,7 +5911,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -6032,16 +5932,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -6133,7 +6033,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C8" s="3">
         <v>4.6</v>
@@ -6147,10 +6047,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="C9" s="3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
@@ -6161,7 +6061,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C10" s="3">
         <v>4.2</v>
@@ -6175,13 +6075,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>4.0</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6189,13 +6089,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="C12" s="3">
         <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6203,7 +6103,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="C13" s="3">
         <v>3.6</v>
@@ -6231,13 +6131,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6245,7 +6145,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>190</v>
+        <v>325</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6271,21 +6171,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3">
@@ -6296,7 +6196,7 @@
         <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4">
@@ -6304,10 +6204,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -6326,7 +6226,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
@@ -6334,7 +6234,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -6342,20 +6242,20 @@
         <v>141</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>238</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>249</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
@@ -6363,10 +6263,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -6385,9 +6285,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="2" max="2" width="59" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6398,10 +6298,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6413,10 +6313,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6433,31 +6333,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>409</v>
+        <v>60</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>410</v>
+        <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>301</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
@@ -6465,31 +6365,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>176</v>
+        <v>417</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4">
@@ -6497,16 +6397,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>420</v>
+        <v>348</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>337</v>
+        <v>166</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -6529,31 +6429,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F5" s="3">
+        <v>96</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="F5" s="3">
-        <v>100</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>426</v>
+        <v>318</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>83</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6">
@@ -6561,31 +6461,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>311</v>
+        <v>425</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>312</v>
+        <v>426</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>313</v>
+        <v>427</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>315</v>
+        <v>430</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>181</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7">
@@ -6593,31 +6493,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>434</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8">
@@ -6625,31 +6525,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>282</v>
+        <v>160</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F8" s="3">
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -6657,28 +6557,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="F9" s="3">
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>117</v>
@@ -6689,31 +6589,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F10" s="3">
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -6721,31 +6621,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="F11" s="3">
         <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12">
@@ -6753,31 +6653,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>305</v>
+        <v>455</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>237</v>
+        <v>345</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="F12" s="3">
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -6785,31 +6685,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F13" s="3">
         <v>68</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="14">
@@ -6817,28 +6717,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>462</v>
+        <v>412</v>
       </c>
       <c r="F14" s="3">
         <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>76</v>
@@ -6849,28 +6749,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F15" s="3">
         <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>117</v>
@@ -6881,31 +6781,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>462</v>
+        <v>412</v>
       </c>
       <c r="F16" s="3">
         <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17">
@@ -6913,31 +6813,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
@@ -6945,31 +6845,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>434</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6977,31 +6877,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>187</v>
+        <v>326</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
@@ -7009,31 +6909,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>311</v>
+        <v>487</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>170</v>
+        <v>488</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="F20" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21">
@@ -7041,31 +6941,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>488</v>
+        <v>125</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>341</v>
+        <v>126</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W42.xlsx
+++ b/reports/devops-jobs-israel-2026-W42.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-14T11:40:08</t>
+    <t xml:space="preserve">2026-10-15T11:17:44</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -498,31 +498,109 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer, DOCA</t>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4468461559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-shavit-software-4478756927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-browser-at-palo-alto-networks-4469323268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4475688590</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4477000056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-paypal-4478324728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deloitte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
   </si>
   <si>
     <t xml:space="preserve">NVIDIA</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-doca-at-nvidia-4478174885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devex-devops-engineer-at-axonius-4446639008</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475656469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vectorious Medical Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4478097565</t>
   </si>
   <si>
     <t xml:space="preserve">Blockaid</t>
@@ -531,81 +609,93 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4478435119</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4468461559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-shavit-software-4478756927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PayPal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-paypal-4478324728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4478097565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deloitte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-deloitte-4479294849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (25769)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-25769-at-yael-group-4474444402</t>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4478094744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4476650305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YouCC Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yaqum, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-youcc-technologies-ltd-4479539731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478503786</t>
   </si>
   <si>
     <t xml:space="preserve">DevOps Engineer (37726)</t>
   </si>
   <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37726-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478516288</t>
   </si>
   <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4478427154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-abra-4477991175</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevOps Engineer-5692</t>
   </si>
   <si>
@@ -618,160 +708,100 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-5692-at-entrypoint-4478139921</t>
   </si>
   <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4478312027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478503786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-specialist-at-comblack-4479012298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475656469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4475688590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4478427154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4478312027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-abra-4477991175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-for-security-team-at-lenovo-4477907387</t>
   </si>
   <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recruitricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4479750646</t>
+  </si>
+  <si>
     <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4477987658</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4478376789</t>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
   </si>
   <si>
     <t xml:space="preserve">Gotfriends</t>
@@ -780,682 +810,652 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4476644367</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SeeTrue AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xsight Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer, Graviton Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4475682981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
     <t xml:space="preserve">GenAI Group DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-03</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersixgill, a Bitsight Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-cybersixgill-a-bitsight-company-4476927366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitsight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-bitsight-4476962715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraCyte Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer - AI Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-ai-security-team-at-lenovo-4477568550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer #8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4476089690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478504540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-medulla-4468207460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
     <t xml:space="preserve">Google</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer, Graviton Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zscaler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-devops-engineer-at-zscaler-4465317702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4475682981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4478094744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraCyte Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer - 244284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-244284-at-experis-israel-4475777772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Developer (DevOps and Infrastructure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-developer-devops-and-infrastructure-at-rapyd-4475489875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend &amp; DevOps Engineer – AI/LLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BlackEdge Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/backend-devops-engineer-%E2%80%93-ai-llm-at-blackedge-labs-4477122203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer #8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4476650305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4476089690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-at-shavit-software-4476766481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478504540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4478769750</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Monitoring, Databases, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-jobgether-4477100901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
@@ -1470,21 +1470,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
     <t xml:space="preserve">SPD Hosting LTD</t>
   </si>
   <si>
@@ -1506,22 +1491,28 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
@@ -1682,7 +1673,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -1690,7 +1681,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1698,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -1706,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10">
@@ -1778,7 +1769,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -1805,55 +1796,39 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>443</v>
+        <v>407</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1869,47 +1844,47 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>498</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>317</v>
+        <v>392</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>394</v>
+        <v>497</v>
       </c>
       <c r="B6" s="3">
         <v>17</v>
@@ -1917,7 +1892,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B7" s="3">
         <v>17</v>
@@ -1925,7 +1900,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
@@ -1933,31 +1908,31 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
@@ -1965,31 +1940,31 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>503</v>
+        <v>386</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>391</v>
+        <v>500</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -2017,13 +1992,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2">
@@ -2034,10 +2009,10 @@
         <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>11.6</v>
+        <v>13.4</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2046,88 +2021,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>61.1</v>
+        <v>35.8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.5</v>
+        <v>32.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.0</v>
+        <v>14.9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2211,7 +2186,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2243,7 +2218,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -2275,7 +2250,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -2307,7 +2282,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -2339,7 +2314,7 @@
         <v>51</v>
       </c>
       <c r="J6" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -2371,7 +2346,7 @@
         <v>58</v>
       </c>
       <c r="J7" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -2403,7 +2378,7 @@
         <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -2435,7 +2410,7 @@
         <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -2467,7 +2442,7 @@
         <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -2499,7 +2474,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -2531,7 +2506,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -2563,7 +2538,7 @@
         <v>83</v>
       </c>
       <c r="J13" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -2595,7 +2570,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -2627,7 +2602,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -2659,7 +2634,7 @@
         <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -2691,7 +2666,7 @@
         <v>101</v>
       </c>
       <c r="J17" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -2723,7 +2698,7 @@
         <v>91</v>
       </c>
       <c r="J18" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -2755,7 +2730,7 @@
         <v>64</v>
       </c>
       <c r="J19" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -2787,7 +2762,7 @@
         <v>111</v>
       </c>
       <c r="J20" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -2819,7 +2794,7 @@
         <v>117</v>
       </c>
       <c r="J21" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -2851,7 +2826,7 @@
         <v>87</v>
       </c>
       <c r="J22" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23">
@@ -2883,7 +2858,7 @@
         <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -2915,7 +2890,7 @@
         <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2947,7 +2922,7 @@
         <v>134</v>
       </c>
       <c r="J25" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -2979,7 +2954,7 @@
         <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -3009,7 +2984,7 @@
         <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -3041,7 +3016,7 @@
         <v>51</v>
       </c>
       <c r="J28" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
@@ -3073,7 +3048,7 @@
         <v>76</v>
       </c>
       <c r="J29" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
@@ -3105,7 +3080,7 @@
         <v>158</v>
       </c>
       <c r="J30" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
@@ -3119,10 +3094,10 @@
         <v>161</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
@@ -3135,7 +3110,7 @@
         <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -3149,10 +3124,10 @@
         <v>166</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
@@ -3162,21 +3137,21 @@
         <v>167</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>48</v>
@@ -3189,27 +3164,27 @@
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>42</v>
@@ -3219,18 +3194,18 @@
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="J34" s="3">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>176</v>
@@ -3242,7 +3217,7 @@
         <v>141</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
@@ -3255,7 +3230,7 @@
         <v>179</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3266,7 +3241,7 @@
         <v>181</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
@@ -3285,18 +3260,18 @@
         <v>129</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>48</v>
@@ -3309,54 +3284,54 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J37" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>48</v>
@@ -3372,24 +3347,24 @@
         <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="J39" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>37</v>
@@ -3399,24 +3374,24 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>129</v>
+        <v>191</v>
       </c>
       <c r="J40" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>195</v>
+        <v>46</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>48</v>
@@ -3429,42 +3404,40 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="J41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>201</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="J42" s="3">
         <v>48</v>
@@ -3472,46 +3445,46 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>37</v>
@@ -3521,27 +3494,27 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>42</v>
@@ -3551,60 +3524,60 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="J45" s="3">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J46" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D47" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3617,18 +3590,18 @@
         <v>129</v>
       </c>
       <c r="J47" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>141</v>
@@ -3644,15 +3617,15 @@
         <v>216</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>217</v>
@@ -3661,7 +3634,7 @@
         <v>166</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>37</v>
@@ -3674,7 +3647,7 @@
         <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J49" s="3">
         <v>1</v>
@@ -3688,7 +3661,7 @@
         <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>48</v>
@@ -3704,10 +3677,10 @@
         <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="J50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3715,56 +3688,56 @@
         <v>222</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="J51" s="3">
-        <v>68</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="D52" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="J52" s="3">
         <v>1</v>
@@ -3772,16 +3745,16 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>37</v>
@@ -3791,10 +3764,10 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="J53" s="3">
         <v>2</v>
@@ -3802,105 +3775,103 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>46</v>
+        <v>164</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>234</v>
+        <v>129</v>
       </c>
       <c r="J54" s="3">
-        <v>36</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="J55" s="3">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="I56" s="3" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>48</v>
@@ -3908,7 +3879,9 @@
       <c r="E57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
@@ -3916,24 +3889,24 @@
         <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="D58" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3943,27 +3916,27 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>245</v>
+        <v>179</v>
       </c>
       <c r="J58" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="C59" s="3" t="s">
-        <v>248</v>
+        <v>171</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>249</v>
+        <v>48</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>42</v>
@@ -3973,27 +3946,27 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="J59" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>175</v>
+        <v>248</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>37</v>
@@ -4003,54 +3976,54 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="D61" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>257</v>
+        <v>179</v>
       </c>
       <c r="J61" s="3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>259</v>
+        <v>220</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>48</v>
@@ -4063,24 +4036,24 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>261</v>
+        <v>168</v>
       </c>
       <c r="J62" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>48</v>
@@ -4093,27 +4066,27 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>117</v>
+        <v>260</v>
       </c>
       <c r="J63" s="3">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>265</v>
+        <v>213</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>249</v>
+        <v>141</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>37</v>
@@ -4123,87 +4096,89 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J65" s="3">
-        <v>61</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="J66" s="3">
-        <v>48</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>276</v>
+        <v>184</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4213,27 +4188,27 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="J67" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>42</v>
@@ -4243,27 +4218,27 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>282</v>
+        <v>179</v>
       </c>
       <c r="J68" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>283</v>
+        <v>222</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>166</v>
+        <v>277</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>37</v>
@@ -4273,40 +4248,40 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>286</v>
+        <v>191</v>
       </c>
       <c r="J69" s="3">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>46</v>
+        <v>164</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>48</v>
+        <v>206</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>117</v>
+        <v>266</v>
       </c>
       <c r="J70" s="3">
         <v>6</v>
@@ -4314,76 +4289,76 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>160</v>
+        <v>282</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="J71" s="3">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>293</v>
+        <v>187</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>296</v>
+        <v>87</v>
       </c>
       <c r="J72" s="3">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>166</v>
+        <v>254</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>37</v>
@@ -4393,27 +4368,27 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>179</v>
       </c>
       <c r="J73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>166</v>
+        <v>293</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>37</v>
@@ -4423,114 +4398,114 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="J74" s="3">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>249</v>
+        <v>141</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="J75" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>71</v>
+        <v>302</v>
       </c>
       <c r="J76" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>175</v>
+        <v>303</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>161</v>
+        <v>286</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>129</v>
+        <v>305</v>
       </c>
       <c r="J77" s="3">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>48</v>
@@ -4543,72 +4518,70 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>46</v>
+        <v>308</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>166</v>
+        <v>254</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="J79" s="3">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>314</v>
+        <v>164</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>316</v>
+        <v>184</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>317</v>
-      </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="J80" s="3">
         <v>3</v>
@@ -4616,13 +4589,13 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>319</v>
+        <v>46</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>48</v>
@@ -4635,24 +4608,24 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="J81" s="3">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>52</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>48</v>
@@ -4665,116 +4638,116 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>326</v>
+        <v>171</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>261</v>
+        <v>179</v>
       </c>
       <c r="J83" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>284</v>
+        <v>321</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>166</v>
+        <v>322</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>330</v>
+        <v>191</v>
       </c>
       <c r="J84" s="3">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>326</v>
+        <v>243</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>332</v>
-      </c>
+      <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="J85" s="3">
-        <v>5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>48</v>
@@ -4787,89 +4760,87 @@
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>179</v>
+        <v>51</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>337</v>
+        <v>52</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>254</v>
+        <v>331</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>255</v>
+        <v>171</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>249</v>
+        <v>48</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>338</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>340</v>
+        <v>191</v>
       </c>
       <c r="J87" s="3">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>46</v>
+        <v>333</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>223</v>
+        <v>335</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>123</v>
+        <v>266</v>
       </c>
       <c r="J88" s="3">
-        <v>58</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>345</v>
+        <v>171</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>37</v>
@@ -4879,40 +4850,42 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>117</v>
+        <v>339</v>
       </c>
       <c r="J89" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>166</v>
+        <v>335</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>117</v>
+        <v>266</v>
       </c>
       <c r="J90" s="3">
         <v>6</v>
@@ -4920,43 +4893,43 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>175</v>
+        <v>343</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>224</v>
+        <v>48</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>261</v>
+        <v>168</v>
       </c>
       <c r="J91" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>353</v>
+        <v>239</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>48</v>
@@ -4964,32 +4937,34 @@
       <c r="E92" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J92" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>37</v>
@@ -4999,27 +4974,27 @@
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>179</v>
+        <v>352</v>
       </c>
       <c r="J93" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>358</v>
+        <v>292</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>161</v>
+        <v>353</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
@@ -5029,57 +5004,59 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="J94" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>200</v>
+        <v>326</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>356</v>
+      </c>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>163</v>
+        <v>358</v>
       </c>
       <c r="J95" s="3">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>363</v>
+        <v>220</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>172</v>
+        <v>360</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>37</v>
@@ -5089,10 +5066,10 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="J96" s="3">
         <v>2</v>
@@ -5100,48 +5077,46 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>367</v>
+        <v>184</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F97" s="3" t="s">
-        <v>317</v>
-      </c>
+      <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J97" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>37</v>
@@ -5151,57 +5126,59 @@
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="J98" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>176</v>
+        <v>369</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J99" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>192</v>
+        <v>373</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>37</v>
@@ -5211,10 +5188,10 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="J100" s="3">
         <v>2</v>
@@ -5222,13 +5199,13 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>377</v>
+        <v>212</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>141</v>
@@ -5241,79 +5218,47 @@
         <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="J101" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>238</v>
+        <v>378</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>166</v>
+        <v>213</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>201</v>
-      </c>
+      <c r="F102" s="3"/>
       <c r="G102" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="J102" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="J103" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J103"/>
+  <autoFilter ref="A1:J102"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5416,7 +5361,6 @@
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
     <hyperlink ref="H102" r:id="rId101"/>
-    <hyperlink ref="H103" r:id="rId102"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5424,8 +5368,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5458,13 +5402,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>159</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5472,18 +5416,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>208</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5491,18 +5435,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5510,18 +5454,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>169</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>175</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5529,18 +5473,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>195</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5548,18 +5492,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>205</v>
+        <v>269</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>206</v>
+        <v>270</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5567,18 +5511,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>207</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>272</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5586,18 +5530,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>175</v>
+        <v>288</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5605,18 +5549,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>200</v>
+        <v>315</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5624,11 +5568,49 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>361</v>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5639,6 +5621,8 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5652,15 +5636,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>201</v>
+        <v>240</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5668,7 +5652,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5676,7 +5660,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5684,7 +5668,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -5700,7 +5684,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -5708,7 +5692,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5716,7 +5700,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5724,7 +5708,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5732,7 +5716,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5740,7 +5724,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5748,7 +5732,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5756,7 +5740,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5764,7 +5748,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5772,7 +5756,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5794,7 +5778,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
@@ -5815,15 +5799,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5831,7 +5815,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5839,7 +5823,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5847,7 +5831,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5855,7 +5839,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5871,15 +5855,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>238</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5887,7 +5871,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5895,7 +5879,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5903,7 +5887,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5911,7 +5895,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B16" s="3">
         <v>2</v>
@@ -5932,16 +5916,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
@@ -6019,13 +6003,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>47</v>
+        <v>239</v>
       </c>
       <c r="C7" s="3">
-        <v>6.0</v>
+        <v>6.2</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -6033,13 +6017,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>238</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3">
-        <v>4.6</v>
+        <v>6.0</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6047,7 +6031,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="C9" s="3">
         <v>4.2</v>
@@ -6061,13 +6045,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6075,10 +6059,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C11" s="3">
-        <v>4.0</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
         <v>3</v>
@@ -6089,13 +6073,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>131</v>
+        <v>212</v>
       </c>
       <c r="C12" s="3">
         <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6103,13 +6087,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>192</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D13" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6117,13 +6101,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>326</v>
       </c>
       <c r="C14" s="3">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6131,10 +6115,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C15" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6145,7 +6129,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C16" s="3">
         <v>2.6</v>
@@ -6171,21 +6155,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -6193,10 +6177,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4">
@@ -6204,10 +6188,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -6226,7 +6210,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
@@ -6234,7 +6218,7 @@
         <v>48</v>
       </c>
       <c r="B2" s="3">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -6242,31 +6226,31 @@
         <v>141</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>244</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>249</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B6" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6285,8 +6269,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="59" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6298,10 +6282,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6313,10 +6297,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6333,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>60</v>
@@ -6342,22 +6326,22 @@
         <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
@@ -6365,31 +6349,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>296</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4">
@@ -6397,28 +6381,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>83</v>
@@ -6429,31 +6413,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>314</v>
+        <v>421</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>315</v>
+        <v>422</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>316</v>
+        <v>171</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F5" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>318</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>185</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6">
@@ -6461,31 +6445,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>425</v>
+        <v>320</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F6" s="3">
+        <v>96</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="F6" s="3">
-        <v>88</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>429</v>
-      </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>430</v>
+        <v>324</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>431</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7">
@@ -6493,31 +6477,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F7" s="3">
-        <v>84</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8">
@@ -6525,31 +6509,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>160</v>
+        <v>435</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>272</v>
+        <v>436</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F8" s="3">
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>439</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>440</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
@@ -6557,28 +6541,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="F9" s="3">
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>117</v>
@@ -6589,31 +6573,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F10" s="3">
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -6621,31 +6605,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F11" s="3">
+        <v>70</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="F11" s="3">
-        <v>74</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>440</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
@@ -6653,31 +6637,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F12" s="3">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="F12" s="3">
-        <v>70</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -6694,22 +6678,22 @@
         <v>460</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F13" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>461</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>462</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>463</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14">
@@ -6717,28 +6701,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F14" s="3">
         <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>76</v>
@@ -6749,16 +6733,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F15" s="3">
         <v>57</v>
@@ -6787,13 +6771,13 @@
         <v>472</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>55</v>
+        <v>335</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F16" s="3">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>473</v>
@@ -6805,7 +6789,7 @@
         <v>474</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>261</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
@@ -6813,31 +6797,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>161</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="F17" s="3">
         <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="18">
@@ -6851,10 +6835,10 @@
         <v>480</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F18" s="3">
         <v>46</v>
@@ -6877,19 +6861,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>326</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="F19" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>485</v>
@@ -6901,7 +6885,7 @@
         <v>486</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>83</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20">
@@ -6912,28 +6896,28 @@
         <v>487</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F20" s="3">
+        <v>34</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F20" s="3">
-        <v>36</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>491</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -6941,31 +6925,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F21" s="3">
+        <v>28</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F21" s="3">
-        <v>34</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>494</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>143</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W42.xlsx
+++ b/reports/devops-jobs-israel-2026-W42.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-15T11:17:44</t>
+    <t xml:space="preserve">2026-10-16T11:12:43</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -663,13 +663,10 @@
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478503786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37726)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37726-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478516288</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4479812979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
   </si>
   <si>
     <t xml:space="preserve">Moveo Source</t>
@@ -765,6 +762,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
   </si>
   <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer - Base44</t>
   </si>
   <si>
@@ -849,6 +861,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
   </si>
   <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cisco</t>
   </si>
   <si>
@@ -858,52 +882,49 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
   </si>
   <si>
-    <t xml:space="preserve">Commit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commit-4477482711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
     <t xml:space="preserve">SRE Tech Lead</t>
@@ -918,27 +939,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
   </si>
   <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Engineer - Edge Team</t>
   </si>
   <si>
@@ -954,15 +954,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
   </si>
   <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4475682981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
   </si>
   <si>
@@ -972,6 +963,78 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
   </si>
   <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer - AI Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-ai-security-team-at-lenovo-4477568550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
   </si>
   <si>
@@ -981,6 +1044,60 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer #8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead &amp; Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yanolja Go Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-architect-at-yanolja-go-global-4476647765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -990,517 +1107,373 @@
     <t xml:space="preserve">North District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
   </si>
   <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraCyte Analytics</t>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4477094134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-infrastructure-engineer-at-teracyte-analytics-4475993753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLOps &amp; Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/mlops-cloud-engineer-at-teracyte-analytics-4476201360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-ai-security-team-at-lenovo-4477568550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer #8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4476089690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer (37652)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-37652-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478504540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-medulla-4468207460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Monitoring, Databases, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-jobgether-4477100901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPD Hosting LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-spd-hosting-ltd-4476095499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Roles requiring it</t>
@@ -1673,7 +1646,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7">
@@ -1681,7 +1654,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1689,7 +1662,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1697,7 +1670,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="10">
@@ -1769,7 +1742,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -1796,39 +1769,55 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>441</v>
+        <v>396</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1844,130 +1833,130 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>486</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>392</v>
+        <v>357</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>497</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>499</v>
+        <v>381</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>389</v>
+        <v>490</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>386</v>
+        <v>491</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1992,13 +1981,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2">
@@ -2009,10 +1998,10 @@
         <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2021,88 +2010,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3">
-        <v>35.8</v>
+        <v>52.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.4</v>
+        <v>8.9</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.1</v>
+        <v>30.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>20.5</v>
+        <v>21.8</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2186,7 +2175,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2218,7 +2207,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2250,7 +2239,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2282,7 +2271,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -2314,7 +2303,7 @@
         <v>51</v>
       </c>
       <c r="J6" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -2346,7 +2335,7 @@
         <v>58</v>
       </c>
       <c r="J7" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -2378,7 +2367,7 @@
         <v>64</v>
       </c>
       <c r="J8" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -2410,7 +2399,7 @@
         <v>51</v>
       </c>
       <c r="J9" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -2442,7 +2431,7 @@
         <v>71</v>
       </c>
       <c r="J10" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -2474,7 +2463,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -2506,7 +2495,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -2538,7 +2527,7 @@
         <v>83</v>
       </c>
       <c r="J13" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -2570,7 +2559,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -2602,7 +2591,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -2634,7 +2623,7 @@
         <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -2666,7 +2655,7 @@
         <v>101</v>
       </c>
       <c r="J17" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -2698,7 +2687,7 @@
         <v>91</v>
       </c>
       <c r="J18" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -2730,7 +2719,7 @@
         <v>64</v>
       </c>
       <c r="J19" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -2762,7 +2751,7 @@
         <v>111</v>
       </c>
       <c r="J20" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -2794,7 +2783,7 @@
         <v>117</v>
       </c>
       <c r="J21" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -2826,7 +2815,7 @@
         <v>87</v>
       </c>
       <c r="J22" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -2858,7 +2847,7 @@
         <v>123</v>
       </c>
       <c r="J23" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
@@ -2890,7 +2879,7 @@
         <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2922,7 +2911,7 @@
         <v>134</v>
       </c>
       <c r="J25" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
@@ -2954,7 +2943,7 @@
         <v>137</v>
       </c>
       <c r="J26" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -2984,7 +2973,7 @@
         <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -3016,7 +3005,7 @@
         <v>51</v>
       </c>
       <c r="J28" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -3048,7 +3037,7 @@
         <v>76</v>
       </c>
       <c r="J29" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30">
@@ -3080,7 +3069,7 @@
         <v>158</v>
       </c>
       <c r="J30" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
@@ -3110,7 +3099,7 @@
         <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -3140,7 +3129,7 @@
         <v>168</v>
       </c>
       <c r="J32" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3170,7 +3159,7 @@
         <v>173</v>
       </c>
       <c r="J33" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -3200,7 +3189,7 @@
         <v>129</v>
       </c>
       <c r="J34" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -3230,7 +3219,7 @@
         <v>179</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3260,7 +3249,7 @@
         <v>129</v>
       </c>
       <c r="J36" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -3290,7 +3279,7 @@
         <v>186</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -3320,7 +3309,7 @@
         <v>51</v>
       </c>
       <c r="J38" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39">
@@ -3350,7 +3339,7 @@
         <v>191</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -3380,7 +3369,7 @@
         <v>191</v>
       </c>
       <c r="J40" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -3410,7 +3399,7 @@
         <v>186</v>
       </c>
       <c r="J41" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -3440,7 +3429,7 @@
         <v>111</v>
       </c>
       <c r="J42" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
@@ -3470,7 +3459,7 @@
         <v>76</v>
       </c>
       <c r="J43" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -3500,7 +3489,7 @@
         <v>191</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -3530,7 +3519,7 @@
         <v>186</v>
       </c>
       <c r="J45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3560,7 +3549,7 @@
         <v>179</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3587,21 +3576,21 @@
         <v>214</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="J47" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>215</v>
+        <v>164</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>141</v>
@@ -3614,100 +3603,100 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="J48" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>164</v>
+        <v>218</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="J49" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>168</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="J51" s="3">
         <v>2</v>
@@ -3715,32 +3704,32 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>225</v>
+        <v>164</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="J52" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3748,13 +3737,13 @@
         <v>164</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>37</v>
@@ -3764,51 +3753,51 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>129</v>
+        <v>234</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>46</v>
+        <v>164</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>171</v>
@@ -3817,28 +3806,28 @@
         <v>48</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>235</v>
+        <v>129</v>
       </c>
       <c r="J55" s="3">
-        <v>37</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>171</v>
@@ -3847,17 +3836,19 @@
         <v>48</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="J56" s="3">
         <v>3</v>
@@ -3865,64 +3856,62 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>238</v>
+        <v>164</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>240</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>179</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3930,7 +3919,7 @@
         <v>46</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>171</v>
@@ -3946,10 +3935,10 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
@@ -3957,32 +3946,32 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>248</v>
+        <v>46</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="J60" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3993,26 +3982,26 @@
         <v>253</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>254</v>
+        <v>171</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="I61" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -4020,13 +4009,13 @@
         <v>256</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>171</v>
+        <v>258</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>42</v>
@@ -4036,21 +4025,21 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J62" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>171</v>
@@ -4059,20 +4048,20 @@
         <v>48</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>260</v>
+        <v>168</v>
       </c>
       <c r="J63" s="3">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4080,13 +4069,13 @@
         <v>164</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>37</v>
@@ -4096,43 +4085,43 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>186</v>
+        <v>264</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>263</v>
+        <v>164</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>266</v>
+        <v>186</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4140,7 +4129,7 @@
         <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>239</v>
+        <v>268</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>171</v>
@@ -4149,33 +4138,31 @@
         <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>240</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>129</v>
+        <v>270</v>
       </c>
       <c r="J66" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>48</v>
@@ -4183,35 +4170,37 @@
       <c r="E67" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>239</v>
+      </c>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
@@ -4224,51 +4213,51 @@
         <v>179</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>222</v>
+        <v>276</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="J69" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>164</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>206</v>
+        <v>48</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
@@ -4278,27 +4267,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>281</v>
+        <v>221</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>171</v>
+        <v>285</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>37</v>
@@ -4308,57 +4297,57 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>284</v>
+        <v>191</v>
       </c>
       <c r="J71" s="3">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>187</v>
+        <v>288</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="J72" s="3">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>37</v>
@@ -4368,147 +4357,147 @@
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="J73" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>292</v>
+        <v>187</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>141</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>129</v>
+        <v>297</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>297</v>
+        <v>171</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="J75" s="3">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>302</v>
+        <v>264</v>
       </c>
       <c r="J76" s="3">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>286</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>305</v>
+        <v>168</v>
       </c>
       <c r="J77" s="3">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>171</v>
+        <v>258</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>37</v>
@@ -4518,57 +4507,57 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>168</v>
       </c>
       <c r="J78" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>254</v>
+        <v>171</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J79" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>164</v>
+        <v>314</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4578,21 +4567,21 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>129</v>
+        <v>317</v>
       </c>
       <c r="J80" s="3">
-        <v>3</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>258</v>
+        <v>318</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>171</v>
@@ -4608,21 +4597,21 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="J81" s="3">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>171</v>
@@ -4631,28 +4620,28 @@
         <v>48</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>179</v>
+        <v>322</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>171</v>
@@ -4668,42 +4657,42 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>321</v>
+        <v>238</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>322</v>
+        <v>171</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>323</v>
+        <v>239</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>191</v>
+        <v>129</v>
       </c>
       <c r="J84" s="3">
         <v>4</v>
@@ -4711,16 +4700,16 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>37</v>
@@ -4730,117 +4719,119 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J85" s="3">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>171</v>
+        <v>332</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>51</v>
+        <v>179</v>
       </c>
       <c r="J86" s="3">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>52</v>
+        <v>334</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>335</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>191</v>
+        <v>337</v>
       </c>
       <c r="J87" s="3">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>335</v>
+        <v>171</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="J88" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>300</v>
+        <v>219</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>171</v>
+        <v>342</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>37</v>
@@ -4850,56 +4841,54 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>339</v>
+        <v>168</v>
       </c>
       <c r="J89" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>335</v>
+        <v>184</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F90" s="3" t="s">
-        <v>341</v>
-      </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>266</v>
+        <v>129</v>
       </c>
       <c r="J90" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>171</v>
+        <v>349</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>48</v>
@@ -4912,151 +4901,151 @@
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="J91" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>239</v>
+        <v>352</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>240</v>
-      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>129</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>352</v>
+        <v>129</v>
       </c>
       <c r="J93" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>292</v>
+        <v>360</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>244</v>
+        <v>141</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>357</v>
+      </c>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="J94" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>356</v>
-      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>358</v>
+        <v>215</v>
       </c>
       <c r="J95" s="3">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>220</v>
+        <v>367</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>360</v>
+        <v>213</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>37</v>
@@ -5066,199 +5055,17 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="J96" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J97" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J98" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J99" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J100" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J101" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J102" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J96"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5355,12 +5162,6 @@
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5368,8 +5169,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5402,13 +5203,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>211</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5416,7 +5217,7 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
@@ -5424,10 +5225,10 @@
         <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5435,18 +5236,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5454,18 +5255,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>347</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>246</v>
+        <v>348</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>171</v>
+        <v>349</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5473,18 +5274,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>247</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>252</v>
+        <v>363</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>364</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>254</v>
+        <v>184</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5492,137 +5293,17 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5636,15 +5317,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5652,7 +5333,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5660,7 +5341,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="B4" s="3">
         <v>20</v>
@@ -5668,7 +5349,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
@@ -5684,7 +5365,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -5692,7 +5373,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5700,7 +5381,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5708,7 +5389,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5716,7 +5397,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5724,7 +5405,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5732,7 +5413,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5740,7 +5421,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5748,7 +5429,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5756,7 +5437,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5769,7 +5450,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5778,7 +5459,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
@@ -5799,7 +5480,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5831,7 +5512,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5839,23 +5520,23 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>212</v>
+        <v>47</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5863,7 +5544,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5871,7 +5552,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>170</v>
+        <v>291</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5879,7 +5560,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5887,7 +5568,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5895,10 +5576,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>300</v>
+        <v>54</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5909,23 +5590,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
@@ -6003,7 +5684,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C7" s="3">
         <v>6.2</v>
@@ -6031,7 +5712,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C9" s="3">
         <v>4.2</v>
@@ -6059,13 +5740,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6073,13 +5754,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="C12" s="3">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6087,10 +5768,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="C13" s="3">
-        <v>3.0</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -6101,10 +5782,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>326</v>
+        <v>170</v>
       </c>
       <c r="C14" s="3">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6115,10 +5796,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>258</v>
+        <v>187</v>
       </c>
       <c r="C15" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>2</v>
@@ -6129,10 +5810,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>334</v>
+        <v>291</v>
       </c>
       <c r="C16" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
@@ -6155,21 +5836,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3">
@@ -6177,10 +5858,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4">
@@ -6191,7 +5872,7 @@
         <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6210,7 +5891,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2">
@@ -6226,12 +5907,12 @@
         <v>141</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B4" s="3">
         <v>8</v>
@@ -6247,15 +5928,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6270,7 +5951,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -6282,10 +5963,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6297,10 +5978,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6317,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>60</v>
@@ -6326,19 +6007,19 @@
         <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>168</v>
@@ -6349,31 +6030,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
@@ -6381,31 +6062,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>83</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
@@ -6413,31 +6094,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>425</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6">
@@ -6445,31 +6126,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>320</v>
+        <v>415</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>321</v>
+        <v>416</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>322</v>
+        <v>417</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>324</v>
+        <v>419</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
@@ -6477,31 +6158,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>429</v>
+        <v>171</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8">
@@ -6509,31 +6190,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>434</v>
+        <v>359</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>435</v>
+        <v>360</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>436</v>
+        <v>361</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>438</v>
+        <v>362</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9">
@@ -6541,31 +6222,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>350</v>
+        <v>428</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>117</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10">
@@ -6573,31 +6254,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>171</v>
+        <v>435</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>448</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -6605,31 +6286,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>309</v>
+        <v>187</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>441</v>
+        <v>402</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>83</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12">
@@ -6637,31 +6318,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>454</v>
+        <v>250</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>457</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
@@ -6669,31 +6350,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>460</v>
+        <v>171</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="F13" s="3">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>186</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14">
@@ -6701,31 +6382,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>171</v>
+        <v>250</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="F14" s="3">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>76</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15">
@@ -6733,31 +6414,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>468</v>
+        <v>309</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F15" s="3">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -6765,31 +6446,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>335</v>
+        <v>459</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="F16" s="3">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>186</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17">
@@ -6797,31 +6478,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>478</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6829,31 +6510,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
@@ -6861,31 +6542,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>484</v>
+        <v>55</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="F19" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>168</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20">
@@ -6893,31 +6574,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>125</v>
+        <v>476</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
@@ -6925,28 +6606,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>171</v>
+        <v>481</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>413</v>
+        <v>443</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>83</v>

--- a/reports/devops-jobs-israel-2026-W42.xlsx
+++ b/reports/devops-jobs-israel-2026-W42.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-16T11:12:43</t>
+    <t xml:space="preserve">2026-10-18T10:52:59</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Architect</t>
+    <t xml:space="preserve">Developer Advocate</t>
   </si>
   <si>
     <t xml:space="preserve">Jfrog</t>
@@ -207,144 +207,135 @@
     <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
     <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
   </si>
   <si>
@@ -588,826 +579,856 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
   </si>
   <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-startup-4475656469</t>
+    <t xml:space="preserve">Blockaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4478435119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4480881694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4476650305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (37047)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4479812979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4478427154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer-5692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entrypoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-5692-at-entrypoint-4478139921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lenovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-for-security-team-at-lenovo-4477907387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4479674975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4477987658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4476644367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Technical Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fig Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4480868969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SeeTrue AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gness-4479919415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xsight Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer לארגון פיננסי מוביל במרכז הארץ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%D7%9C%D7%90%D7%A8%D7%92%D7%95%D7%9F-%D7%A4%D7%99%D7%A0%D7%A0%D7%A1%D7%99-%D7%9E%D7%95%D7%91%D7%99%D7%9C-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%90%D7%A8%D7%A5-at-jobist-4477738635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or HaNer, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Leader - Cloud Platform &amp; SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/group-leader-cloud-platform-sre-at-confidential-4478209649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer, Graviton Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lendbuzz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer - AI Security Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-ai-security-team-at-lenovo-4477568550</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ScaleOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer #8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesnet Group Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-confidential-careers-4478210872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead &amp; Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yanolja Go Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-architect-at-yanolja-go-global-4476647765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandisk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Linux Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weizmann Institute of Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Vectorious Medical Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-vectorious-medical-technologies-4478097565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blockaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-blockaid-4478435119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4478094744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4476650305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YouCC Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yaqum, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-youcc-technologies-ltd-4479539731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer (37047)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-37047-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4479812979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveo Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-moveo-source-4478427154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4477992588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4477094134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior HPC DevOps Engineer, NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-hpc-devops-engineer-ncs-at-nvidia-4453261687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT System Administrator 243902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4478225096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-abra-4477991175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer-5692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entrypoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-5692-at-entrypoint-4478139921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4478312027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4475677766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frame Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-frame-security-4462248477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-workiz-4478519240</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer - AI for Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lenovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-ai-for-security-team-at-lenovo-4477907387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4479824052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zenity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4478465745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-check-point-software-4479304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4479116905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-base44-at-base44-4474179911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recruitricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-recruitricks-4479750646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer — Cybersecurity business unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-%E2%80%94-cybersecurity-business-unit-at-drivenets-4477987658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4476644367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Technical Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fig Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-technical-lead-at-fig-security-4475988067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-ai-security-team-at-lenovo-4477578131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SeeTrue AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-devops-engineer-at-seetrue-ai-4477069152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps &amp; AI Enablement Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xsight Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-ai-enablement-engineer-at-xsight-labs-4471491552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-cisco-4478317023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-confidential-careers-4476662621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or HaNer, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-tairc-4475660825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE) On-Prem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-on-prem-at-dream-4463814798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-edge-team-at-lenovo-4477910328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer, Graviton Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-graviton-team-at-amazon-4478568501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer (Infra Platform)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-infra-platform-at-monday-com-4479587116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-engineer-at-mind-4477244856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lendbuzz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-engineer-at-lendbuzz-4477980904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer - AI Security Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-ai-security-team-at-lenovo-4477568550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice (Formerly ActiveFence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-alice-formerly-activefence-4472729462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4476601079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer Team Lead - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-team-lead-il-at-scaleops-4479538658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4478103033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer #8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tesnet Group Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-%238106-at-tesnet-group-ltd-4478384662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead &amp; Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yanolja Go Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-cloud-architect-at-yanolja-go-global-4476647765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Integration &amp; Infrastructure Engineer (Advanced storage infrastructure for AI workloads)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandisk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-integration-infrastructure-engineer-advanced-storage-infrastructure-for-ai-workloads-at-sandisk-4478351208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Linux Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weizmann Institute of Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-linux-administrator-at-weizmann-institute-of-science-4475664301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4477094134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Administrator (5515)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INGIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-administrator-5515-at-ingima-4476707352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novocure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
   </si>
   <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
@@ -1446,33 +1467,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -1488,10 +1482,10 @@
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Terraform/IaC</t>
@@ -1646,7 +1640,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -1654,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1662,7 +1656,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -1670,7 +1664,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>866</v>
+        <v>854</v>
       </c>
     </row>
     <row r="10">
@@ -1750,7 +1744,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1769,12 +1763,12 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -1782,7 +1776,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>443</v>
+        <v>394</v>
       </c>
       <c r="B3" s="3">
         <v>9</v>
@@ -1790,23 +1784,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>406</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1814,7 +1808,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>408</v>
+        <v>482</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1833,23 +1827,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B3" s="3">
         <v>26</v>
@@ -1857,23 +1851,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="B6" s="3">
         <v>22</v>
@@ -1881,7 +1875,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
@@ -1889,7 +1883,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>381</v>
+        <v>488</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
@@ -1897,7 +1891,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>490</v>
+        <v>379</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
@@ -1905,10 +1899,10 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -1916,36 +1910,36 @@
         <v>371</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -1953,7 +1947,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B16" s="3">
         <v>7</v>
@@ -1981,13 +1975,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="2">
@@ -1995,13 +1989,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>12.9</v>
+        <v>12.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2010,88 +2004,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
-        <v>52.1</v>
+        <v>43.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.4</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.9</v>
+        <v>34.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2175,7 +2169,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -2207,7 +2201,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -2239,7 +2233,7 @@
         <v>40</v>
       </c>
       <c r="J4" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -2271,7 +2265,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -2303,7 +2297,7 @@
         <v>51</v>
       </c>
       <c r="J6" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -2335,7 +2329,7 @@
         <v>58</v>
       </c>
       <c r="J7" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -2352,7 +2346,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>62</v>
@@ -2364,15 +2358,15 @@
         <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="J8" s="3">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>60</v>
@@ -2384,22 +2378,22 @@
         <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J9" s="3">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -2407,10 +2401,10 @@
         <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>48</v>
@@ -2419,27 +2413,27 @@
         <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J10" s="3">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>48</v>
@@ -2451,27 +2445,27 @@
         <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="J11" s="3">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>48</v>
@@ -2495,7 +2489,7 @@
         <v>79</v>
       </c>
       <c r="J12" s="3">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -2503,7 +2497,7 @@
         <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>48</v>
@@ -2527,7 +2521,7 @@
         <v>83</v>
       </c>
       <c r="J13" s="3">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -2535,7 +2529,7 @@
         <v>84</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>48</v>
@@ -2559,7 +2553,7 @@
         <v>87</v>
       </c>
       <c r="J14" s="3">
-        <v>50</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -2567,10 +2561,10 @@
         <v>88</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>48</v>
@@ -2579,30 +2573,30 @@
         <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J15" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>48</v>
@@ -2623,7 +2617,7 @@
         <v>97</v>
       </c>
       <c r="J16" s="3">
-        <v>29</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
@@ -2631,16 +2625,16 @@
         <v>98</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>99</v>
@@ -2652,21 +2646,21 @@
         <v>100</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="J17" s="3">
-        <v>81</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>48</v>
@@ -2675,19 +2669,19 @@
         <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="J18" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
@@ -2695,16 +2689,16 @@
         <v>105</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>106</v>
@@ -2716,85 +2710,85 @@
         <v>107</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="J19" s="3">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J20" s="3">
-        <v>49</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="J21" s="3">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>48</v>
@@ -2803,91 +2797,91 @@
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="J22" s="3">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J23" s="3">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J24" s="3">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>48</v>
@@ -2896,10 +2890,10 @@
         <v>48</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
@@ -2911,7 +2905,7 @@
         <v>134</v>
       </c>
       <c r="J25" s="3">
-        <v>56</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -2919,228 +2913,226 @@
         <v>135</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J26" s="3">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="J27" s="3">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J28" s="3">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="J29" s="3">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>156</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J30" s="3">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J31" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J32" s="3">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>171</v>
+        <v>55</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>48</v>
@@ -3156,24 +3148,24 @@
         <v>172</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>173</v>
+        <v>126</v>
       </c>
       <c r="J33" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>42</v>
@@ -3186,24 +3178,24 @@
         <v>175</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>42</v>
@@ -3213,30 +3205,30 @@
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="D36" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
@@ -3246,7 +3238,7 @@
         <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="J36" s="3">
         <v>4</v>
@@ -3254,19 +3246,19 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
@@ -3276,10 +3268,10 @@
         <v>185</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>186</v>
+        <v>51</v>
       </c>
       <c r="J37" s="3">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38">
@@ -3287,10 +3279,10 @@
         <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>48</v>
@@ -3303,30 +3295,30 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>51</v>
+        <v>183</v>
       </c>
       <c r="J38" s="3">
-        <v>66</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>189</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
@@ -3336,21 +3328,21 @@
         <v>190</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>48</v>
@@ -3366,24 +3358,24 @@
         <v>193</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J40" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>46</v>
+        <v>195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>48</v>
+        <v>197</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>42</v>
@@ -3393,27 +3385,27 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J41" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>37</v>
@@ -3423,70 +3415,70 @@
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="J42" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="J43" s="3">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="J44" s="3">
         <v>5</v>
@@ -3494,16 +3486,16 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>206</v>
+        <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>42</v>
@@ -3513,87 +3505,87 @@
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>211</v>
+        <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>37</v>
@@ -3603,24 +3595,24 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="J48" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>48</v>
@@ -3628,32 +3620,34 @@
       <c r="E49" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J49" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>141</v>
+        <v>226</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>37</v>
@@ -3663,10 +3657,10 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="J50" s="3">
         <v>3</v>
@@ -3674,13 +3668,13 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>46</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>226</v>
+        <v>168</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>48</v>
@@ -3693,73 +3687,73 @@
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3767,10 +3761,10 @@
         <v>46</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>48</v>
@@ -3783,24 +3777,24 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="J54" s="3">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>48</v>
@@ -3813,24 +3807,24 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>129</v>
+        <v>240</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>48</v>
@@ -3838,34 +3832,32 @@
       <c r="E56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>239</v>
-      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J56" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>37</v>
@@ -3878,51 +3870,51 @@
         <v>244</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>46</v>
+        <v>248</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>48</v>
@@ -3935,87 +3927,89 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>46</v>
+        <v>252</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>250</v>
+        <v>168</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>215</v>
+        <v>126</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>252</v>
+        <v>46</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="J61" s="3">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>42</v>
@@ -4028,10 +4022,10 @@
         <v>259</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>179</v>
+        <v>67</v>
       </c>
       <c r="J62" s="3">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63">
@@ -4039,26 +4033,26 @@
         <v>260</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="J63" s="3">
         <v>3</v>
@@ -4066,13 +4060,13 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>48</v>
@@ -4085,73 +4079,73 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>264</v>
+        <v>194</v>
       </c>
       <c r="J64" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="J66" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4159,42 +4153,40 @@
         <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>239</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>48</v>
@@ -4207,57 +4199,57 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>179</v>
+        <v>277</v>
       </c>
       <c r="J68" s="3">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>171</v>
+        <v>284</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>37</v>
@@ -4267,27 +4259,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>283</v>
+        <v>126</v>
       </c>
       <c r="J70" s="3">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>221</v>
+        <v>286</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>285</v>
+        <v>201</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>37</v>
@@ -4297,117 +4289,117 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J71" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>288</v>
+        <v>184</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>179</v>
+        <v>292</v>
       </c>
       <c r="J72" s="3">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>129</v>
+        <v>245</v>
       </c>
       <c r="J73" s="3">
-        <v>4</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>187</v>
+        <v>221</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>295</v>
+        <v>168</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="J74" s="3">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>171</v>
+        <v>280</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4417,13 +4409,13 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="J75" s="3">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -4431,13 +4423,13 @@
         <v>302</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>303</v>
+        <v>167</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>304</v>
+        <v>168</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>42</v>
@@ -4447,40 +4439,40 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="J76" s="3">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="J77" s="3">
         <v>3</v>
@@ -4488,76 +4480,78 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="C78" s="3" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="J78" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>313</v>
-      </c>
       <c r="I79" s="3" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="J79" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>37</v>
@@ -4567,62 +4561,64 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J80" s="3">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>312</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>171</v>
+        <v>225</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>48</v>
+        <v>226</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
@@ -4633,7 +4629,7 @@
         <v>322</v>
       </c>
       <c r="J82" s="3">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83">
@@ -4644,7 +4640,7 @@
         <v>324</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>48</v>
@@ -4660,7 +4656,7 @@
         <v>325</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="J83" s="3">
         <v>3</v>
@@ -4671,42 +4667,40 @@
         <v>326</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>171</v>
+        <v>327</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>239</v>
-      </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="J84" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>250</v>
+        <v>181</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>48</v>
@@ -4719,32 +4713,34 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>331</v>
+        <v>126</v>
       </c>
       <c r="J85" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>332</v>
+        <v>201</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F86" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
@@ -4752,10 +4748,10 @@
         <v>333</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="J86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4763,31 +4759,29 @@
         <v>334</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>242</v>
+        <v>336</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>335</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>337</v>
+        <v>203</v>
       </c>
       <c r="J87" s="3">
-        <v>47</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -4798,7 +4792,7 @@
         <v>339</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>48</v>
@@ -4806,32 +4800,34 @@
       <c r="E88" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>179</v>
+        <v>342</v>
       </c>
       <c r="J88" s="3">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>219</v>
+        <v>344</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>342</v>
+        <v>158</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>37</v>
@@ -4841,87 +4837,91 @@
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="J89" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>184</v>
+        <v>348</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>349</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J90" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F91" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>215</v>
+        <v>355</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>37</v>
@@ -4931,141 +4931,107 @@
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="J92" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>355</v>
+        <v>184</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>357</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>129</v>
+        <v>277</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>361</v>
+        <v>201</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>357</v>
-      </c>
+      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="J94" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="J95" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J96" s="3">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J96"/>
+  <autoFilter ref="A1:J95"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5161,7 +5127,6 @@
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
     <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5169,8 +5134,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5203,13 +5168,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5217,7 +5182,7 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
@@ -5225,10 +5190,10 @@
         <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5236,7 +5201,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4">
@@ -5244,10 +5209,10 @@
         <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5255,18 +5220,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>347</v>
+        <v>161</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>349</v>
+        <v>181</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5274,18 +5239,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>350</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>363</v>
+        <v>268</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>364</v>
+        <v>269</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5293,17 +5258,77 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>365</v>
       </c>
+      <c r="C9" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>366</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5317,15 +5342,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3">
         <v>21</v>
@@ -5333,7 +5358,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5341,23 +5366,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B4" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B6" s="3">
         <v>12</v>
@@ -5365,31 +5390,31 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
@@ -5397,7 +5422,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5405,15 +5430,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B13" s="3">
         <v>9</v>
@@ -5421,7 +5446,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5429,7 +5454,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5437,7 +5462,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5459,12 +5484,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -5472,7 +5497,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5480,7 +5505,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -5496,7 +5521,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5504,7 +5529,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5512,7 +5537,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5520,15 +5545,15 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>207</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5536,7 +5561,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5544,7 +5569,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5552,7 +5577,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5560,7 +5585,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5568,7 +5593,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5597,16 +5622,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2">
@@ -5614,7 +5639,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C2" s="3">
         <v>23.8</v>
@@ -5628,7 +5653,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
         <v>18.6</v>
@@ -5642,10 +5667,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C4" s="3">
-        <v>10.1</v>
+        <v>9.2</v>
       </c>
       <c r="D4" s="3">
         <v>3</v>
@@ -5656,10 +5681,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3">
-        <v>9.2</v>
+        <v>7.1</v>
       </c>
       <c r="D5" s="3">
         <v>3</v>
@@ -5670,13 +5695,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -5684,7 +5709,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="C7" s="3">
         <v>6.2</v>
@@ -5712,7 +5737,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C9" s="3">
         <v>4.2</v>
@@ -5726,7 +5751,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5740,13 +5765,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5754,13 +5779,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>315</v>
+        <v>184</v>
       </c>
       <c r="C12" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5768,13 +5793,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>145</v>
+        <v>279</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -5782,13 +5807,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>3.0</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5796,13 +5821,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5810,7 +5835,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5836,21 +5861,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3">
@@ -5858,10 +5883,10 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4">
@@ -5869,10 +5894,10 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -5891,7 +5916,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
@@ -5904,7 +5929,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -5912,31 +5937,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>243</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5950,7 +5975,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="2" max="2" width="59" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -5963,10 +5988,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -5978,10 +6003,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -5998,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>60</v>
@@ -6007,22 +6032,22 @@
         <v>61</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
@@ -6030,31 +6055,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="4">
@@ -6062,31 +6087,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="5">
@@ -6094,31 +6119,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>412</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="J5" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -6126,31 +6151,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F6" s="3">
         <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>419</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7">
@@ -6158,31 +6183,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>421</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F7" s="3">
         <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="8">
@@ -6190,31 +6215,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F8" s="3">
         <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>191</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -6222,31 +6247,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="F9" s="3">
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="10">
@@ -6254,31 +6279,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F10" s="3">
         <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>437</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -6286,31 +6311,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F11" s="3">
         <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>440</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12">
@@ -6318,31 +6343,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="F12" s="3">
         <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>445</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
@@ -6350,31 +6375,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>447</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F13" s="3">
         <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="14">
@@ -6382,31 +6407,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="F14" s="3">
         <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15">
@@ -6414,31 +6439,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F15" s="3">
         <v>70</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>456</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6446,31 +6471,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F16" s="3">
+        <v>70</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="F16" s="3">
-        <v>68</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>462</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -6478,31 +6503,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="F17" s="3">
+        <v>68</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="F17" s="3">
-        <v>61</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6510,31 +6535,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>68</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="F18" s="3">
-        <v>57</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19">
@@ -6542,31 +6567,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F19" s="3">
+        <v>61</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="F19" s="3">
-        <v>54</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>474</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>270</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -6574,31 +6599,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="F20" s="3">
+        <v>57</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="F20" s="3">
-        <v>46</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>478</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
@@ -6606,31 +6631,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F21" s="3">
+        <v>54</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="F21" s="3">
-        <v>39</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>83</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
